--- a/data/trans_orig/P6904-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6904-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>31524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28260</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34089</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49679</t>
+          <t>49455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24013</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61986</t>
+          <t>61906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83473</t>
+          <t>81533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37531</t>
+          <t>37537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64080</t>
+          <t>64217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54327</t>
+          <t>54800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73855</t>
+          <t>73337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>62379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84378</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45703</t>
+          <t>45230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31938</t>
+          <t>32441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53044</t>
+          <t>53937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103401</t>
+          <t>104644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131857</t>
+          <t>134807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35801</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130964</t>
+          <t>130225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162374</t>
+          <t>160967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>66022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97428</t>
+          <t>96185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88401</t>
+          <t>89808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119811</t>
+          <t>120550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>39656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48993</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84181</t>
+          <t>84452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40050</t>
+          <t>40696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67344</t>
+          <t>68734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246734</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113916</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360650</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334291</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>216</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225571</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106205</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331777</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>246734</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>223693</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>268198</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>52,24%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>113916</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>100160</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>129872</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>45,5%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>59,0%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>360650</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>333659</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>386773</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>48,19%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>55,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>225571</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>204107</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>248612</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47,76%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>106205</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>90249</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>119961</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>54,5%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>331777</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>305654</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>358768</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>47,92%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>44,14%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>51,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31467</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49333</t>
+          <t>49069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47827</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67924</t>
+          <t>67055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29496</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46509</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33091</t>
+          <t>32360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50816</t>
+          <t>50683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51303</t>
+          <t>50585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73266</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61790</t>
+          <t>62508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61765</t>
+          <t>62612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82029</t>
+          <t>82401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46706</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96096</t>
+          <t>96747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122615</t>
+          <t>123713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>52588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37340</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>59441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87058</t>
+          <t>86407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29073</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62546</t>
+          <t>62038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178441</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196372</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288825</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147014</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103278</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>250291</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325455</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325455</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325455</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>196</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>508</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539116</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539116</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539116</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>178441</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>160143</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>197915</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>54,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,21%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>60,81%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>110383</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>94801</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>124703</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>58,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>288825</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>264194</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>312849</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>53,57%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>58,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>147014</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>127540</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>165312</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45,17%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,19%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>50,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>103278</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>88958</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>118860</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>48,34%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>41,64%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>55,63%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>250291</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>226267</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>274922</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>41,97%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>50,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>325455</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>325455</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>325455</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>213661</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>213661</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>213661</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>539116</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>539116</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>539116</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>28008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>30006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>33874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29365</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59506</t>
+          <t>58971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42848</t>
+          <t>42822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32722</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29928</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45828</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36403</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55193</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36962</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40056</t>
+          <t>40448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77003</t>
+          <t>77211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99303</t>
+          <t>99769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>51494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67834</t>
+          <t>67765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134464</t>
+          <t>134049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162736</t>
+          <t>162066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59866</t>
+          <t>59658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58210</t>
+          <t>58880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>86897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35612</t>
+          <t>35139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52348</t>
+          <t>52072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>29245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41129</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69715</t>
+          <t>69872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89586</t>
+          <t>90622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>25797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46704</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>193</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208440</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189315</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>228223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145362</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158949</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>331</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353802</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331123</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141561</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70936</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212497</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>208440</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>189336</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>227259</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>59,55%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>131567</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>67,2%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>60,83%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>73,65%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>353802</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>330461</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>377016</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>62,48%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>58,35%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>66,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>141561</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>122742</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>160665</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>40,45%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>45,9%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>70936</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>56985</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>84731</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>32,8%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>26,35%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>212497</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>189283</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>235838</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>37,52%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>33,42%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>41,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13817</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>34776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58523</t>
+          <t>58545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24281</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46583</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>65542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25122</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50476</t>
+          <t>50297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>36957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>42640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60492</t>
+          <t>61336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>43974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58846</t>
+          <t>58811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>77054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101277</t>
+          <t>100930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55098</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138218</t>
+          <t>140470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168559</t>
+          <t>168938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>56164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32164</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50660</t>
+          <t>49539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70417</t>
+          <t>70038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100758</t>
+          <t>98506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>32780</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45254</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90370</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117318</t>
+          <t>116698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128978</t>
+          <t>129197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159932</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36877</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49438</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208774</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188962</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227403</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230727</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>439501</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412105</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>483970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130731</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112102</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121565</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>252296</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>208774</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>188867</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>227692</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61,49%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>55,63%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>230727</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>209752</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>262226</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>65,49%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>59,54%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>74,43%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>439501</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>411545</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>478538</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>59,49%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>130731</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>111813</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>150638</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,51%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>121565</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>90066</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>142540</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>40,46%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>252296</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>213259</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>280252</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>40,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
